--- a/schema/Copaf/issues_metadados_copaf.xlsx
+++ b/schema/Copaf/issues_metadados_copaf.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T104"/>
+  <dimension ref="A1:T107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>COD_CAE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CNAE associado ao Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FK_DECRETO_R_CNAE_DECRETO (FOREIGN KEY: ENABLED)- SYS_C00119077 (C: ENABLED)</t>
+          <t>FK_CAE_R_CNAE_DECRETO (FOREIGN KEY: ENABLED)- PK_CNAE_DECRETO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525954 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>22</v>
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="b">
         <v>1</v>
@@ -622,7 +622,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COD_CAE</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FK_CAE_R_CNAE_DECRETO (FOREIGN KEY: ENABLED)- SYS_C00119079 (C: ENABLED)</t>
+          <t>FK_DECRETO_R_CNAE_DECRETO (FOREIGN KEY: ENABLED)- PK_CNAE_DECRETO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525953 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>22</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="b">
         <v>1</v>
@@ -698,12 +698,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO_DECRETO</t>
+          <t>DAT_FIM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SYS_C002015394 (C: ENABLED)- SYS_C002015396 (PRIMARY KEY: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -722,37 +722,37 @@
         </is>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DAT_FIM</t>
+          <t>DAT_INICIO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>7</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DAT_INICIO</t>
+          <t>SEQ_DEBITO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>FK_DEBITO_R_DEBITO_DEC (FOREIGN KEY: ENABLED)- SYS_C001563775 (C: ENABLED)- SYS_C001563776 (PRIMARY KEY: ENABLED)- UK_DEBITO_DECRETO_1 (UNIQUE: ENABLED)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="S6" t="b">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="b">
+      <c r="T6" t="b">
         <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -926,7 +926,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO</t>
+          <t>SEQ_DEBITO_DECRETO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UK_DEBITO_DECRETO_1 (UNIQUE: ENABLED)</t>
+          <t>SYS_C001563875 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>22</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>SEQ_DECRETO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK_DECRETO_R_DEBITO_DEC (FOREIGN KEY: ENABLED)- SYS_C002015395 (C: ENABLED)- UK_DEBITO_DECRETO_1 (UNIQUE: ENABLED)</t>
+          <t>FK_DECRETO_R_DEBITO_DEC (FOREIGN KEY: ENABLED)- SYS_C001563774 (C: ENABLED)- SYS_C001563776 (PRIMARY KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>22</v>
@@ -1035,34 +1035,34 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="b">
-        <v>0</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
       </c>
       <c r="T8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SEQ_USUARIO</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK_USUARIO_R_DEBITO_DEC (FOREIGN KEY: ENABLED)</t>
+          <t>SYS_C001563876 (C: ENABLED)- UK_DEBITO_DECRETO_1 (UNIQUE: ENABLED)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>22</v>
@@ -1111,34 +1111,34 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
         <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>1</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO_PARCELAMENTO</t>
+          <t>DEBITO_DECRETO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO_DECRETO_PARCELAMENTO</t>
+          <t>SEQ_USUARIO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SYS_C002022587 (C: ENABLED)- SYS_C002022590 (PRIMARY KEY: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>22</v>
@@ -1187,10 +1187,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>788</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>788</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
@@ -1342,7 +1342,7 @@
         <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>788</v>
       </c>
       <c r="I13" t="n">
         <v>22</v>
@@ -1418,7 +1418,7 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>525</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEQ_USUARIO</t>
+          <t>SEQ_DEBITO_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SYS_C002022588 (C: ENABLED)</t>
+          <t>SYS_C001563957 (C: ENABLED)- SYS_C001563959 (PRIMARY KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>788</v>
       </c>
       <c r="I14" t="n">
         <v>22</v>
@@ -1491,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>788</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK_DECRETO_R_DEBITO_DECRETO_PARC (FOREIGN KEY: ENABLED)- SYS_C002022589 (C: ENABLED)</t>
+          <t>FK_DECRETO_R_DEBITO_DECRETO_PARC (FOREIGN KEY: ENABLED)- SYS_C001563958 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>788</v>
       </c>
       <c r="I15" t="n">
         <v>22</v>
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEBITO_PARCELAMENTO</t>
+          <t>DEBITO_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEQ_PARCELAMENTO</t>
+          <t>SEQ_USUARIO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK_PARCELAMENTO_R_DEBITO_PAR (FOREIGN KEY: ENABLED)- SYS_C00106331 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>207</v>
+        <v>788</v>
       </c>
       <c r="I16" t="n">
         <v>22</v>
@@ -1643,13 +1643,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do D�bito baixado atrav�s do Parcelamento</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK_DEBITO_R_DEBITO_PAR (FOREIGN KEY: ENABLED)- SYS_C00106332 (C: ENABLED)</t>
+          <t>FK_DEBITO_R_DEBITO_PAR (FOREIGN KEY: ENABLED)- PK_DEBITO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525957 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>207</v>
+        <v>242762</v>
       </c>
       <c r="I17" t="n">
         <v>22</v>
@@ -1722,7 +1722,7 @@
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>207</v>
+        <v>242304</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="b">
         <v>1</v>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>DEBITO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>SEQ_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Parcelamento</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PK_DECRETO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C00111404 (C: ENABLED)</t>
+          <t>FK_PARCELAMENTO_R_DEBITO_PAR (FOREIGN KEY: ENABLED)- PK_DEBITO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525956 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>242762</v>
       </c>
       <c r="I18" t="n">
         <v>22</v>
@@ -1795,10 +1795,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>15</v>
+        <v>21310</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -1838,17 +1838,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DAT_FIM</t>
+          <t>COD_INDICADOR_MINIMO_PARCELA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C�digo do indicar financeiro para o campo VLR_MINIMO_PARCELA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1862,22 +1862,22 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1914,22 +1914,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DAT_INICIO</t>
+          <t>COD_ORIGEM_DECRETO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sistema de origem do D�bito. Mesma codifica��o do campo CONTA_CORRENTE.DEBITO.TIP_ORIGEM_SISTEMA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SYS_C00111405 (C: ENABLED)</t>
+          <t>DECRETO_PARCELAMENTO_UK1 (UNIQUE: ENABLED)- SYS_C001525962 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1938,19 +1938,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NUM_DECRETO</t>
+          <t>COD_TIPO_ATUALIZACAO_PARCELA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tipo de atualiza��o da parcela</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO_UK1 (UNIQUE: ENABLED)- SYS_C00111406 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I21" t="n">
-        <v>256</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>COD_ORIGEM_DECRETO</t>
+          <t>COD_TIPO_DECRETO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tipo do Decreto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO_UK1 (UNIQUE: ENABLED)- SYS_C00111407 (C: ENABLED)</t>
+          <t>DECRETO_PARCELAMENTO_UK1 (UNIQUE: ENABLED)- SYS_C001525964 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
@@ -2099,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2142,17 +2142,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DSC_ANO_MES_PRIM_PARCELA</t>
+          <t>COD_TIPO_VENCIMENTO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Codigo do tipo vencimento
+1- Ultimo dia util
+2- Data da abertura</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2166,22 +2168,22 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2218,17 +2220,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DSC_PERIODO_REFERENCIA_FIM</t>
+          <t>DAT_FIM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data final da vig�ncia do decreto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2242,7 +2244,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I24" t="n">
         <v>7</v>
@@ -2251,13 +2253,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2294,22 +2296,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DSC_PERIODO_REFERENCIA_INICIO</t>
+          <t>DAT_INICIO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data de in�cio da vig�ncia do decreto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001525960 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2318,7 +2320,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I25" t="n">
         <v>7</v>
@@ -2327,13 +2329,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2342,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -2370,22 +2372,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>QTD_PARCELAS</t>
+          <t>DSC_ANO_MES_PRIM_PARCELA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>M�s e Ano (MM/AAAA) de vencimento definido para a primeira parcela dos parcelamentos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SYS_C00111408 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2394,22 +2396,22 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2418,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -2446,22 +2448,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>COD_TIPO_DECRETO</t>
+          <t>DSC_PERIODO_REFERENCIA_FIM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>M�s e Ano (MM/AAAA) final a que se referem os d�bitos pass�veis de serem parcelados</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO_UK1 (UNIQUE: ENABLED)- SYS_C00111409 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2470,22 +2472,22 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2494,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -2506,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2522,22 +2524,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NUM_MAXIMO_DIAS_ATRASO</t>
+          <t>DSC_PERIODO_REFERENCIA_INICIO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>M�s e Ano (MM/AAAA) inicial a que se referem os d�bitos pass�veis de serem parcelados</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SYS_C00111410 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2546,22 +2548,22 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2570,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -2598,22 +2600,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VLR_DESCONTO_JUROS</t>
+          <t>DSC_PER_REF_INICIO_MESES_CONSE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Per�odo de refer�ncia inicial. Ano e M�s</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SYS_C00133222 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2622,10 +2624,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2637,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2674,22 +2676,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VLR_DESCONTO_MULTA</t>
+          <t>NUM_DECRETO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N�mero do Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SYS_C00133223 (C: ENABLED)</t>
+          <t>DECRETO_PARCELAMENTO_UK1 (UNIQUE: ENABLED)- SYS_C001525961 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2698,22 +2700,22 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2722,19 +2724,19 @@
         <v>0</v>
       </c>
       <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="b">
         <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2750,7 +2752,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VLR_MINIMO_PARCELA</t>
+          <t>NUM_MAXIMO_DIAS_ATRASO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2760,12 +2762,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Valor m�nimo de cada parcela</t>
+          <t>N�mero m�ximo de dias de atraso permitido no pagamento das parcelas deste novo parcelamento</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SYS_C00111411 (C: ENABLED)</t>
+          <t>SYS_C001525965 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2774,19 +2776,19 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I31" t="n">
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2826,7 +2828,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COD_INDICADOR_MINIMO_PARCELA</t>
+          <t>NUM_PERCENTUAL_1A_PARCELA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2836,7 +2838,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C�digo do indicador financeiro utilizado para o campo VLR_MINIMO_PARCELA</t>
+          <t>Percentual utilizado para 1a parcela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2850,22 +2852,22 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I32" t="n">
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2902,7 +2904,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NUM_PERCENTUAL_1A_PARCELA</t>
+          <t>NUM_PERIODOS_CONSEC_ATRASO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2912,12 +2914,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Percentual utilizado para a primeira parcela do parcelamento</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SYS_C00133226 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2926,22 +2928,22 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I33" t="n">
         <v>22</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2978,7 +2980,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COD_TIPO_VENCIMENTO</t>
+          <t>QTD_PARCELAS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2988,12 +2990,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quantidade de parcelas a serem aplicadas, como definidas no decreto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001525963 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3002,7 +3004,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I34" t="n">
         <v>22</v>
@@ -3011,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3026,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
@@ -3054,22 +3056,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TIP_CRITICA_CNAE</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>PK_DECRETO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525959 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3078,37 +3080,37 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I35" t="n">
+        <v>22</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>43</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
         <v>1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" t="b">
-        <v>0</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -3130,12 +3132,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TIP_CRITICA_RECEITA</t>
+          <t>STA_VERIFICA_3_MESES_CONSEC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3154,22 +3156,22 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3206,7 +3208,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DSC_PER_REF_INICIO_MESES_CONSE</t>
+          <t>TIP_CRITICA_CNAE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3216,7 +3218,9 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tipo de cr�tica para CNAE:
+'I' - Inclus�o
+'E' - Exclus�o</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3230,22 +3234,22 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3282,17 +3286,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>COD_TIPO_ATUALIZACAO_PARCELA</t>
+          <t>TIP_CRITICA_RECEITA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tipo de cr�tica para C�digo de Receita:
+'I' - Inclus�o
+'E' - Exclus�o</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3306,22 +3312,22 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3382,7 +3388,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I39" t="n">
         <v>255</v>
@@ -3391,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3434,7 +3440,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STA_VERIFICA_3_MESES_CONSEC</t>
+          <t>VLR_MINIMO_PARCELA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3444,12 +3450,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Valor m�nimo de cada parcela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001527004 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3458,22 +3464,22 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I40" t="n">
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -3482,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
@@ -3505,12 +3511,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>DESCONTO_REFIS_DAE_MIGRADO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NUM_PERIODOS_CONSEC_ATRASO</t>
+          <t>SEQ_DESCONTO_REFIS_DAE_MIGRADO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3520,12 +3526,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do registro de Desconto</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>PK_DESCONTO_REFIS_DAE_MIGRADO (PRIMARY KEY: ENABLED)- SYS_C001526193 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3534,7 +3540,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>15</v>
+        <v>35324</v>
       </c>
       <c r="I41" t="n">
         <v>22</v>
@@ -3543,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>35324</v>
       </c>
       <c r="M41" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3558,13 +3564,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
         <v>1</v>
-      </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="b">
-        <v>0</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3586,7 +3592,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SEQ_DESCONTO_REFIS_DAE_MIGRADO</t>
+          <t>SEQ_DOCUMENTO_CREDITO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3596,12 +3602,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Campo chave primaria da tabela que ir� utilizar a sequence SEQ_DOCUMENTO_CREDITO.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SYS_C00133909 (PRIMARY KEY: ENABLED)- SYS_C0082679 (C: ENABLED)</t>
+          <t>FK_DOC_CRED_R_DESC_DAE_REF_LEG (FOREIGN KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3610,7 +3616,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>35324</v>
       </c>
       <c r="I42" t="n">
         <v>22</v>
@@ -3619,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>10</v>
+        <v>35272</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3634,16 +3640,16 @@
         <v>0</v>
       </c>
       <c r="P42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
       <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
         <v>1</v>
-      </c>
-      <c r="S42" t="b">
-        <v>0</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
@@ -3672,12 +3678,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Valor de desconto sobre juros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SYS_C00133906 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3686,7 +3692,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>35324</v>
       </c>
       <c r="I43" t="n">
         <v>22</v>
@@ -3698,7 +3704,7 @@
         <v>5</v>
       </c>
       <c r="L43" t="n">
-        <v>10</v>
+        <v>19988</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3748,12 +3754,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Valor de desconto sobre multa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SYS_C00133907 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3762,7 +3768,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>35324</v>
       </c>
       <c r="I44" t="n">
         <v>22</v>
@@ -3774,7 +3780,7 @@
         <v>5</v>
       </c>
       <c r="L44" t="n">
-        <v>9</v>
+        <v>6106</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3824,12 +3830,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Valor de desconto sobre valor principal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SYS_C00133908 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3838,7 +3844,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>35324</v>
       </c>
       <c r="I45" t="n">
         <v>22</v>
@@ -3850,7 +3856,7 @@
         <v>3</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3885,17 +3891,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DESCONTO_REFIS_DAE_MIGRADO</t>
+          <t>FAIXA_DESCONTO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SEQ_DOCUMENTO_CREDITO</t>
+          <t>DAT_FIM_ADESAO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3905,7 +3911,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FK_DOC_CRED_R_DESC_DAE_REF_LEG (FOREIGN KEY: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3914,19 +3920,19 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3947,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="b">
         <v>0</v>
@@ -3966,12 +3972,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SEQ_FAIXA_DESCONTO</t>
+          <t>DAT_INICIO_ADESAO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3981,7 +3987,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SYS_C00138516 (PRIMARY KEY: ENABLED)- SYS_C0084284 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3990,19 +3996,19 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L47" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -4014,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="P47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -4052,12 +4058,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quantidade m�xima de parcelas para entrar nesta faixa de desconto</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SYS_C0084285 (C: ENABLED)</t>
+          <t>SYS_C001525969 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4066,7 +4072,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="I48" t="n">
         <v>22</v>
@@ -4075,10 +4081,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L48" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -4128,12 +4134,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quantidade m�nima de parcelas para entrar nesta faixa de desconto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SYS_C0084286 (C: ENABLED)</t>
+          <t>SYS_C001525970 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4142,7 +4148,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="I49" t="n">
         <v>22</v>
@@ -4154,7 +4160,7 @@
         <v>3</v>
       </c>
       <c r="L49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -4204,12 +4210,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FK_DECRETO_R_FAIXA (FOREIGN KEY: ENABLED)- SYS_C0084287 (C: ENABLED)</t>
+          <t>FK_DECRETO_R_FAIXA (FOREIGN KEY: ENABLED)- SYS_C001525971 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4218,7 +4224,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="I50" t="n">
         <v>22</v>
@@ -4227,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -4270,7 +4276,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VLR_DESCONTO_JUROS</t>
+          <t>SEQ_FAIXA_DESCONTO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4280,12 +4286,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador da faixa de desconto</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SYS_C00138455 (C: ENABLED)</t>
+          <t>PK_FAIXA_DESCONTO (PRIMARY KEY: ENABLED)- SYS_C001525968 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4294,19 +4300,19 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="I51" t="n">
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -4318,13 +4324,13 @@
         <v>0</v>
       </c>
       <c r="P51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R51" t="b">
         <v>1</v>
-      </c>
-      <c r="Q51" t="b">
-        <v>0</v>
-      </c>
-      <c r="R51" t="b">
-        <v>0</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -4346,7 +4352,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VLR_DESCONTO_MULTA</t>
+          <t>VLR_DESCONTO_JUROS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4356,12 +4362,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Percentual de desconto de juros para esta faixa de descontos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SYS_C00138517 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4370,7 +4376,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="I52" t="n">
         <v>22</v>
@@ -4382,7 +4388,7 @@
         <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -4422,17 +4428,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DAT_FIM_ADESAO</t>
+          <t>VLR_DESCONTO_MULTA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Percentual de desconto de multas para esta faixa de descontos</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4446,19 +4452,19 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -4493,27 +4499,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FAIXA_DESCONTO</t>
+          <t>FAIXA_PERCENTUAL_1A_PARCELA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DAT_INICIO_ADESAO</t>
+          <t>NUM_QUANTIDADE_MAX_PARCELAS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N�mero m�ximo de quantidade de parcelas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001528114 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4522,19 +4528,19 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -4546,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
@@ -4574,7 +4580,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SEQ_FAIXA_PERC_1A_PARCELA</t>
+          <t>NUM_QUANTIDADE_MIN_PARCELAS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4584,12 +4590,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N�mero M�nimo de Quantidade de Parcelas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SYS_C00118060 (C: ENABLED)- SYS_C00136406 (PRIMARY KEY: ENABLED)</t>
+          <t>SYS_C001528115 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4598,7 +4604,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I55" t="n">
         <v>22</v>
@@ -4607,10 +4613,10 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -4628,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4650,7 +4656,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VLR_PERCENTUAL_1A_PARCELA</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4660,12 +4666,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SYS_C00136405 (C: ENABLED)</t>
+          <t>FK_FAIXA_PE_FK_DECRET_DECRETO_ (FOREIGN KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4674,19 +4680,19 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I56" t="n">
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>3</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -4707,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="b">
         <v>0</v>
@@ -4726,7 +4732,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NUM_QUANTIDADE_MAX_PARCELAS</t>
+          <t>SEQ_FAIXA_PERC_1A_PARCELA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4736,12 +4742,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador da faixa de desconto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SYS_C00118063 (C: ENABLED)</t>
+          <t>PK_FAIXA_PERCENTUAL_1A_PARCELA (PRIMARY KEY: ENABLED)- SYS_C001528112 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4750,7 +4756,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I57" t="n">
         <v>22</v>
@@ -4762,7 +4768,7 @@
         <v>3</v>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -4780,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="R57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4802,7 +4808,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NUM_QUANTIDADE_MIN_PARCELAS</t>
+          <t>VLR_PERCENTUAL_1A_PARCELA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4812,12 +4818,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Valor do percentual da 1a parcela</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SYS_C00118066 (C: ENABLED)</t>
+          <t>SYS_C001528113 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4826,19 +4832,19 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I58" t="n">
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
         <v>3</v>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -4873,27 +4879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FAIXA_PERCENTUAL_1A_PARCELA</t>
+          <t>LOG_EVENTO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>DAT_LOG_EVENTO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>TIMESTAMP(6)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data/hora de ocorr�ncia do evento</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FK_FAIXA_PERCENTUAL_1A_PARCELA_R_DECRETO_PARCELAMENTO (FOREIGN KEY: ENABLED)- SYS_C00118069 (C: ENABLED)</t>
+          <t>SYS_C001525974 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4902,19 +4908,19 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>31998</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>24186</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -4935,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
@@ -4954,12 +4960,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SEQ_LOG_EVENTO</t>
+          <t>DSC_MENSAGEM</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>CLOB</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4969,7 +4975,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SYS_C00142280 (PRIMARY KEY: ENABLED)- SYS_C0072659 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4978,22 +4984,22 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>4000</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="L60" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>22726</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -5002,13 +5008,13 @@
         <v>0</v>
       </c>
       <c r="P60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -5030,12 +5036,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DAT_LOG_EVENTO</t>
+          <t>DSC_VALOR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6)</t>
+          <t>CLOB</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5045,7 +5051,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SYS_C0072660 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5054,19 +5060,19 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
       <c r="I61" t="n">
-        <v>11</v>
+        <v>4000</v>
       </c>
       <c r="J61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>11</v>
+        <v>1334</v>
       </c>
       <c r="L61" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -5078,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -5106,22 +5112,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TIP_EVENTO</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SYS_C0072661 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5130,22 +5136,22 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
       <c r="I62" t="n">
-        <v>255</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>31953</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -5154,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
@@ -5182,7 +5188,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>SEQ_LOG_EVENTO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5192,12 +5198,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do registro de log</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>PK_LOG_EVENTO (PRIMARY KEY: ENABLED)- SYS_C001525973 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5206,7 +5212,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
       <c r="I63" t="n">
         <v>22</v>
@@ -5215,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L63" t="n">
-        <v>18</v>
+        <v>31998</v>
       </c>
       <c r="M63" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -5230,13 +5236,13 @@
         <v>0</v>
       </c>
       <c r="P63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63" t="b">
         <v>1</v>
-      </c>
-      <c r="Q63" t="b">
-        <v>0</v>
-      </c>
-      <c r="R63" t="b">
-        <v>0</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -5268,7 +5274,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Parcelamento</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5282,7 +5288,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
       <c r="I64" t="n">
         <v>22</v>
@@ -5291,13 +5297,13 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>70</v>
+        <v>21858</v>
       </c>
       <c r="M64" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -5344,7 +5350,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Usu�rio respons�vel pelo evento</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5358,7 +5364,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
       <c r="I65" t="n">
         <v>22</v>
@@ -5367,13 +5373,13 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="M65" t="n">
-        <v>25</v>
+        <v>30407</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -5410,22 +5416,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DSC_VALOR</t>
+          <t>TIP_EVENTO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CLOB</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tipo do evento</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001525975 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5434,19 +5440,19 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
       <c r="I66" t="n">
-        <v>4000</v>
+        <v>255</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1675</v>
+        <v>25</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -5458,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
@@ -5481,17 +5487,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LOG_EVENTO</t>
+          <t>MENSAGEM_DEBITOS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DSC_MENSAGEM</t>
+          <t>DAT_MENSAGEM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CLOB</t>
+          <t>TIMESTAMP(6)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5501,7 +5507,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001560043 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5510,22 +5516,22 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>93</v>
+        <v>1777</v>
       </c>
       <c r="I67" t="n">
-        <v>4000</v>
+        <v>11</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1777</v>
       </c>
       <c r="M67" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -5534,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -5562,12 +5568,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SEQ_MENSAGEM_DEBITOS</t>
+          <t>DSC_IDENTIFICADOR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5577,7 +5583,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SYS_C001594576 (C: ENABLED)- SYS_C001594580 (PRIMARY KEY: ENABLED)</t>
+          <t>SYS_C001560044 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5586,19 +5592,19 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1728</v>
+        <v>1777</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>255</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="L68" t="n">
-        <v>1728</v>
+        <v>1777</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5616,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -5638,12 +5644,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DAT_MENSAGEM</t>
+          <t>DSC_VALOR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6)</t>
+          <t>CLOB</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5653,7 +5659,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SYS_C001594577 (C: ENABLED)</t>
+          <t>SYS_C001560045 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5662,19 +5668,19 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1728</v>
+        <v>1777</v>
       </c>
       <c r="I69" t="n">
-        <v>11</v>
+        <v>4000</v>
       </c>
       <c r="J69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="L69" t="n">
-        <v>1728</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -5714,12 +5720,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DSC_IDENTIFICADOR</t>
+          <t>SEQ_MENSAGEM_DEBITOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5729,7 +5735,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SYS_C001594578 (C: ENABLED)</t>
+          <t>SYS_C001560042 (C: ENABLED)- SYS_C001560046 (PRIMARY KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5738,19 +5744,19 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1728</v>
+        <v>1777</v>
       </c>
       <c r="I70" t="n">
-        <v>255</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="L70" t="n">
-        <v>1728</v>
+        <v>1777</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -5768,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="R70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5785,27 +5791,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MENSAGEM_DEBITOS</t>
+          <t>PARCELA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DSC_VALOR</t>
+          <t>COD_RECEITA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CLOB</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C�digo da Receita</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SYS_C001594579 (C: ENABLED)</t>
+          <t>FK_COD_RECEITA_R_PARCELA (FOREIGN KEY: ENABLED)- SYS_C001525982 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5814,19 +5820,19 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1728</v>
+        <v>463299</v>
       </c>
       <c r="I71" t="n">
-        <v>4000</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>324</v>
+        <v>4</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -5847,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="b">
         <v>0</v>
@@ -5866,22 +5872,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SEQ_PARCELA</t>
+          <t>DAT_VENCIMENTO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data de vencimento da Parcela</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SYS_C00118103 (C: ENABLED)- SYS_C00127582 (PRIMARY KEY: ENABLED)</t>
+          <t>SYS_C001525979 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5890,19 +5896,19 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>461</v>
+        <v>463299</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L72" t="n">
-        <v>461</v>
+        <v>6565</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -5920,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5942,22 +5948,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DAT_VENCIMENTO</t>
+          <t>NUM_PARCELA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N�mero da parcela no Parcelamento</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SYS_C00118104 (C: ENABLED)</t>
+          <t>SYS_C001525980 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5966,19 +5972,19 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>461</v>
+        <v>463299</v>
       </c>
       <c r="I73" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L73" t="n">
-        <v>249</v>
+        <v>120</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -6018,7 +6024,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NUM_PARCELA</t>
+          <t>NUM_PERCENTUAL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6028,12 +6034,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Percentual do valor total do Parcelamento representado por esta parcela, onde 1 representa 100%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SYS_C00118105 (C: ENABLED)</t>
+          <t>SYS_C001525981 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6042,19 +6048,19 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>461</v>
+        <v>463299</v>
       </c>
       <c r="I74" t="n">
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L74" t="n">
-        <v>60</v>
+        <v>23624</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -6094,22 +6100,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NUM_PERCENTUAL</t>
+          <t>SEQ_DOCUMENTO_CREDITO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Documento de Cr�dito</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SYS_C00118107 (C: ENABLED)</t>
+          <t>FK_DOCUMENTO_CREDITO_R_PARCELA (FOREIGN KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6118,7 +6124,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>461</v>
+        <v>463299</v>
       </c>
       <c r="I75" t="n">
         <v>22</v>
@@ -6127,13 +6133,13 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L75" t="n">
-        <v>39</v>
+        <v>130336</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>326790</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -6142,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="b">
         <v>0</v>
@@ -6151,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="b">
         <v>0</v>
@@ -6170,7 +6176,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>COD_RECEITA</t>
+          <t>SEQ_PARCELA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6180,12 +6186,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador de uma Parcela</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FK_COD_RECEITA_R_PARCELA (FOREIGN KEY: ENABLED)- SYS_C00118109 (C: ENABLED)</t>
+          <t>PK_PARCELA (PRIMARY KEY: ENABLED)- SYS_C001525978 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6194,7 +6200,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>461</v>
+        <v>463299</v>
       </c>
       <c r="I76" t="n">
         <v>22</v>
@@ -6203,10 +6209,10 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L76" t="n">
-        <v>3</v>
+        <v>463299</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -6224,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="R76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" t="b">
         <v>0</v>
@@ -6256,12 +6262,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Parcelamento</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FK_PARCELAMENTO_R_PARCELA (FOREIGN KEY: ENABLED)- SYS_C00118115 (C: ENABLED)</t>
+          <t>FK_PARCELAMENTO_R_PARCELA (FOREIGN KEY: ENABLED)- SYS_C001525983 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6270,7 +6276,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>461</v>
+        <v>463299</v>
       </c>
       <c r="I77" t="n">
         <v>22</v>
@@ -6282,7 +6288,7 @@
         <v>6</v>
       </c>
       <c r="L77" t="n">
-        <v>64</v>
+        <v>21546</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -6317,12 +6323,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PARCELA</t>
+          <t>PARCELAMENTO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SEQ_DOCUMENTO_CREDITO</t>
+          <t>COD_ORGAO_LOCAL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6332,12 +6338,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C�digo do �rg�o Local associado ao Contribuinte (caso seja Contribuinte cadastrado de ICMS)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FK_DOCUMENTO_CREDITO_R_PARCELA (FOREIGN KEY: ENABLED)</t>
+          <t>FK_ORG_LOCAL_R_PARCEL (FOREIGN KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6346,7 +6352,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>461</v>
+        <v>21665</v>
       </c>
       <c r="I78" t="n">
         <v>22</v>
@@ -6355,13 +6361,13 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L78" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M78" t="n">
-        <v>444</v>
+        <v>27</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
@@ -6393,12 +6399,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PARCELA</t>
+          <t>PARCELAMENTO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SEQ_DAE_EMITIDO</t>
+          <t>COD_ORGAO_LOCAL_INC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6408,12 +6414,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C�digo do �rg�o Local de cria��o do Parcelamento</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>FK_ORG_LOCAL_INC_R_PARCEL (FOREIGN KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6422,7 +6428,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>461</v>
+        <v>21665</v>
       </c>
       <c r="I79" t="n">
         <v>22</v>
@@ -6431,13 +6437,13 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M79" t="n">
-        <v>461</v>
+        <v>11103</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -6455,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="S79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="b">
         <v>0</v>
@@ -6474,22 +6480,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SEQ_PARCELAMENTO</t>
+          <t>DAT_ABERTURA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data de abertura do Parcelamento</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SYS_C00143763 (PRIMARY KEY: ENABLED)- SYS_C0074076 (C: ENABLED)</t>
+          <t>SYS_C001525986 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6498,19 +6504,19 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L80" t="n">
-        <v>70</v>
+        <v>2417</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -6528,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -6550,22 +6556,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DAT_ABERTURA</t>
+          <t>DAT_FINAL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data final do parcelamento</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SYS_C0074077 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6574,22 +6580,22 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I81" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L81" t="n">
-        <v>24</v>
+        <v>2148</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>9292</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -6598,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
@@ -6626,17 +6632,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DAT_FINAL</t>
+          <t>DSC_HASH_DOCUMENTO_ALFRESCO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6)</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HASH para verificar a integridade do arquivo do Alfresco</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6650,22 +6656,22 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I82" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="J82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L82" t="n">
-        <v>22</v>
+        <v>11837</v>
       </c>
       <c r="M82" t="n">
-        <v>20</v>
+        <v>9828</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -6702,7 +6708,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NUM_PROCESSO</t>
+          <t>DSC_ID_ARQUIVO_TERMO_ALFRESCO</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6712,7 +6718,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ID do arquivo do Termo de Parcelamento, localizado no Alfresco</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6726,7 +6732,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I83" t="n">
         <v>256</v>
@@ -6735,13 +6741,13 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="M83" t="n">
-        <v>70</v>
+        <v>21502</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -6788,7 +6794,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Observa��o registrada sobre o parcelamento</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6802,7 +6808,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I84" t="n">
         <v>4000</v>
@@ -6811,13 +6817,13 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M84" t="n">
-        <v>70</v>
+        <v>21294</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -6854,22 +6860,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QTD_PARCELAS</t>
+          <t>DSC_URL_TERMO_ALFRESCO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>URL referente ao Termo de Parcelamento, localizado no Alfresco</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SYS_C0074078 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6878,10 +6884,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6890,10 +6896,10 @@
         <v>3</v>
       </c>
       <c r="L85" t="n">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>21502</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -6902,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="b">
         <v>0</v>
@@ -6930,22 +6936,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>STA_PARCELAMENTO</t>
+          <t>NUM_PROCESSO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N�mero de processo associado ao Parcelamento</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SYS_C0074079 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6954,22 +6960,22 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L86" t="n">
-        <v>9</v>
+        <v>562</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>11214</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -6978,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="b">
         <v>0</v>
@@ -7006,22 +7012,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>NUM_TERMO_NOTIFICACAO_PERDA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Termo de Notifica��o</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FK_DEC_PAR_R_PARCEL (FOREIGN KEY: ENABLED)- SYS_C0074080 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7030,22 +7036,22 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>21662</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -7054,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
@@ -7063,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="S87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="b">
         <v>0</v>
@@ -7082,7 +7088,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>COD_ORGAO_LOCAL</t>
+          <t>QTD_PARCELAS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7092,12 +7098,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quantidade de parcelas do parcelamento</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FK_ORG_LOCAL_R_PARCEL (FOREIGN KEY: ENABLED)</t>
+          <t>SYS_C001525987 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7106,7 +7112,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I88" t="n">
         <v>22</v>
@@ -7115,10 +7121,10 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L88" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -7130,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
@@ -7139,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" t="b">
         <v>0</v>
@@ -7158,7 +7164,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>COD_ORGAO_LOCAL_INC</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7168,12 +7174,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Decreto de Parcelamento que regulamenta este parcelamento</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FK_ORG_LOCAL_INC_R_PARCEL (FOREIGN KEY: ENABLED)</t>
+          <t>FK_DEC_PAR_R_PARCEL (FOREIGN KEY: ENABLED)- SYS_C001525989 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7182,7 +7188,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I89" t="n">
         <v>22</v>
@@ -7191,13 +7197,13 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="M89" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -7206,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
@@ -7234,7 +7240,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SEQ_PESSOA</t>
+          <t>SEQ_DECRETO_REFIS_A_VISTA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7249,7 +7255,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FK_PESSOA_R_PARCEL (FOREIGN KEY: ENABLED)</t>
+          <t>FK_DEC_VISTA_PAR_R_PARCEL (FOREIGN KEY: ENABLED)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7258,7 +7264,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I90" t="n">
         <v>22</v>
@@ -7267,13 +7273,13 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" t="n">
         <v>6</v>
       </c>
-      <c r="L90" t="n">
-        <v>15</v>
-      </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>17624</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -7310,7 +7316,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SEQ_SOCIO</t>
+          <t>SEQ_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7320,12 +7326,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Parcelamento</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>PK_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525985 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7334,7 +7340,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I91" t="n">
         <v>22</v>
@@ -7343,13 +7349,13 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>21665</v>
       </c>
       <c r="M91" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -7358,13 +7364,13 @@
         <v>0</v>
       </c>
       <c r="P91" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="b">
+        <v>0</v>
+      </c>
+      <c r="R91" t="b">
         <v>1</v>
-      </c>
-      <c r="Q91" t="b">
-        <v>0</v>
-      </c>
-      <c r="R91" t="b">
-        <v>0</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -7386,7 +7392,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>STA_PARCELAMENTO_INTERNET</t>
+          <t>SEQ_PARCELAMENTO_ORIGINAL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7410,7 +7416,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I92" t="n">
         <v>22</v>
@@ -7419,13 +7425,13 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>743</v>
       </c>
       <c r="M92" t="n">
-        <v>7</v>
+        <v>20804</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -7462,22 +7468,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DSC_URL_TERMO_ALFRESCO</t>
+          <t>SEQ_PESSOA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Contribuinte para o qual foi criado este Parcelamento</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>FK_PESSOA_R_PARCEL (FOREIGN KEY: ENABLED)- SYS_C001525991 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7486,22 +7492,22 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I93" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="L93" t="n">
-        <v>15</v>
+        <v>11230</v>
       </c>
       <c r="M93" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -7510,16 +7516,16 @@
         <v>0</v>
       </c>
       <c r="P93" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="b">
+        <v>0</v>
+      </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+      <c r="S93" t="b">
         <v>1</v>
-      </c>
-      <c r="Q93" t="b">
-        <v>0</v>
-      </c>
-      <c r="R93" t="b">
-        <v>0</v>
-      </c>
-      <c r="S93" t="b">
-        <v>0</v>
       </c>
       <c r="T93" t="b">
         <v>0</v>
@@ -7538,22 +7544,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DSC_ID_ARQUIVO_TERMO_ALFRESCO</t>
+          <t>STA_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Situa��o do parcelamento</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001525988 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7562,22 +7568,22 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I94" t="n">
-        <v>256</v>
+        <v>22</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M94" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -7586,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
@@ -7614,17 +7620,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DSC_HASH_DOCUMENTO_ALFRESCO</t>
+          <t>STA_PARCELAMENTO_INTERNET</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Indica se o Parcelamento foi feito na Internet</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7638,22 +7644,22 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
       <c r="I95" t="n">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L95" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -7685,17 +7691,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PER_REF_INICIO_MESES_CONSECUTIVOS</t>
+          <t>COD_RECEITA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7705,7 +7711,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001565296 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7714,22 +7720,22 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>70</v>
+        <v>382935</v>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M96" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -7738,7 +7744,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="b">
         <v>0</v>
@@ -7761,17 +7767,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NUM_TERMO_NOTIFICACAO_PERDA</t>
+          <t>DAT_VENCIMENTO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VARCHAR2</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7781,7 +7787,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001565293 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7790,22 +7796,22 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>70</v>
+        <v>382935</v>
       </c>
       <c r="I97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>6526</v>
       </c>
       <c r="M97" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -7814,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="b">
         <v>0</v>
@@ -7837,12 +7843,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SEQ_PARCELAMENTO_ORIGINAL</t>
+          <t>NUM_PARCELA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7857,7 +7863,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (: )</t>
+          <t>SYS_C001565294 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7866,7 +7872,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>70</v>
+        <v>382935</v>
       </c>
       <c r="I98" t="n">
         <v>22</v>
@@ -7875,13 +7881,13 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L98" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="M98" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -7890,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="b">
         <v>0</v>
@@ -7913,12 +7919,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_REFIS_A_VISTA</t>
+          <t>NUM_PERCENTUAL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7933,7 +7939,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FK_DEC_VISTA_PAR_R_PARCEL (FOREIGN KEY: ENABLED)</t>
+          <t>SYS_C001565295 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7942,22 +7948,22 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>70</v>
+        <v>382935</v>
       </c>
       <c r="I99" t="n">
         <v>22</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>19418</v>
       </c>
       <c r="M99" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
@@ -7966,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
@@ -7975,7 +7981,7 @@
         <v>0</v>
       </c>
       <c r="S99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T99" t="b">
         <v>0</v>
@@ -7989,12 +7995,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RECEITA_DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>SEQ_DOCUMENTO_CREDITO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8009,7 +8015,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FK_DECRETO_R_RECEITA_DECRETO (FOREIGN KEY: ENABLED)- PK_RECEITA_DECRETO_PARCEL (PRIMARY KEY: ENABLED)- SYS_C00120788 (C: ENABLED)</t>
+          <t xml:space="preserve"> (: )</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8018,7 +8024,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>14</v>
+        <v>382935</v>
       </c>
       <c r="I100" t="n">
         <v>22</v>
@@ -8027,13 +8033,13 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L100" t="n">
-        <v>8</v>
+        <v>121528</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>256308</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -8042,16 +8048,16 @@
         <v>0</v>
       </c>
       <c r="P100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T100" t="b">
         <v>0</v>
@@ -8065,12 +8071,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RECEITA_DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>COD_RECEITA</t>
+          <t>SEQ_PARCELA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8085,7 +8091,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FK_RECEITA_R_RECEITA_DECRETO (FOREIGN KEY: ENABLED)- PK_RECEITA_DECRETO_PARCEL (PRIMARY KEY: ENABLED)- SYS_C00120790 (C: ENABLED)</t>
+          <t>PK_PARCELA_S345565 (PRIMARY KEY: ENABLED)- SYS_C001565292 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8094,7 +8100,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>14</v>
+        <v>382935</v>
       </c>
       <c r="I101" t="n">
         <v>22</v>
@@ -8103,10 +8109,10 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L101" t="n">
-        <v>9</v>
+        <v>382935</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -8127,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="S101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" t="b">
         <v>0</v>
@@ -8141,12 +8147,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>REGIME_DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>SEQ_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8161,7 +8167,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FK_DECRETO_R_REGIME_DECRETO (FOREIGN KEY: ENABLED)- SYS_C00106803 (C: ENABLED)</t>
+          <t>SYS_C001565297 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8170,7 +8176,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>382935</v>
       </c>
       <c r="I102" t="n">
         <v>22</v>
@@ -8179,10 +8185,10 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L102" t="n">
-        <v>3</v>
+        <v>16866</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -8203,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T102" t="b">
         <v>0</v>
@@ -8217,12 +8223,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>REGIME_DECRETO_PARCELAMENTO</t>
+          <t>RECEITA_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>COD_REGIME_RECOLHIMENTO</t>
+          <t>COD_RECEITA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8232,12 +8238,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C�digo da Receita</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FK_REGIME_R_REGIME_DECRETO (FOREIGN KEY: ENABLED)- SYS_C00106804 (C: ENABLED)</t>
+          <t>FK_RECEITA_R_RECEITA_DECRETO (FOREIGN KEY: ENABLED)- PK_RECEITA_DECRETO_PARCEL (PRIMARY KEY: ENABLED)- SYS_C001550361 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8246,7 +8252,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="I103" t="n">
         <v>22</v>
@@ -8255,28 +8261,28 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L103" t="n">
+        <v>11</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>0</v>
+      </c>
+      <c r="R103" t="b">
         <v>1</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="b">
-        <v>0</v>
-      </c>
-      <c r="R103" t="b">
-        <v>0</v>
       </c>
       <c r="S103" t="b">
         <v>1</v>
@@ -8293,12 +8299,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TABELA_TESTE</t>
+          <t>RECEITA_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SEQ_TABELA_TESTE</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8308,12 +8314,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sequencial identificador do Decreto de Parcelamento</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SYS_C00129609 (PRIMARY KEY: ENABLED)- SYS_C0089659 (C: ENABLED)</t>
+          <t>FK_DECRETO_R_RECEITA_DECRETO (FOREIGN KEY: ENABLED)- PK_RECEITA_DECRETO_PARCEL (PRIMARY KEY: ENABLED)- SYS_C001550360 (C: ENABLED)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8322,7 +8328,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I104" t="n">
         <v>22</v>
@@ -8331,10 +8337,10 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -8355,9 +8361,237 @@
         <v>1</v>
       </c>
       <c r="S104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>COPAF</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>REGIME_DECRETO_PARCELAMENTO</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>COD_REGIME_RECOLHIMENTO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>C�digo do Regime de Recolhimento associado ao Decreto de Parcelamento</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>FK_REGIME_R_REGIME_DECRETO (FOREIGN KEY: ENABLED)- PK_REGIME_DECRETO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525994 (C: ENABLED)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>22</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>3</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="b">
+        <v>0</v>
+      </c>
+      <c r="R105" t="b">
+        <v>1</v>
+      </c>
+      <c r="S105" t="b">
+        <v>1</v>
+      </c>
+      <c r="T105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>COPAF</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>REGIME_DECRETO_PARCELAMENTO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Sequencial identificador do Decreto de Parcelamento</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>FK_DECRETO_R_REGIME_DECRETO (FOREIGN KEY: ENABLED)- PK_REGIME_DECRETO_PARCELAMENTO (PRIMARY KEY: ENABLED)- SYS_C001525993 (C: ENABLED)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>22</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>3</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="b">
+        <v>0</v>
+      </c>
+      <c r="R106" t="b">
+        <v>1</v>
+      </c>
+      <c r="S106" t="b">
+        <v>1</v>
+      </c>
+      <c r="T106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>COPAF</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TABELA_TESTE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SEQ_TABELA_TESTE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SYS_C001552244 (C: ENABLED)- SYS_C001552245 (PRIMARY KEY: ENABLED)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>22</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>0</v>
+      </c>
+      <c r="R107" t="b">
+        <v>1</v>
+      </c>
+      <c r="S107" t="b">
+        <v>0</v>
+      </c>
+      <c r="T107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8372,7 +8606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8414,7 +8648,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -8434,7 +8668,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -8454,7 +8688,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -8514,7 +8748,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2656</v>
+        <v>1180807</v>
       </c>
     </row>
     <row r="8">
@@ -8530,11 +8764,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Total number of cells in schema</t>
+          <t>Total number of cells in schema (sum of columns x rows for each table)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13931</v>
+        <v>7245802</v>
       </c>
     </row>
     <row r="9">
@@ -8554,7 +8788,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1885</v>
+        <v>834566</v>
       </c>
     </row>
     <row r="10">
@@ -8574,7 +8808,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -8594,7 +8828,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -8614,7 +8848,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -8634,7 +8868,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8654,7 +8888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15">
@@ -8674,7 +8908,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>207</v>
+        <v>242762</v>
       </c>
     </row>
     <row r="16">
@@ -8694,7 +8928,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -8714,7 +8948,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>35324</v>
       </c>
     </row>
     <row r="18">
@@ -8734,7 +8968,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -8754,7 +8988,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -8774,7 +9008,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>93</v>
+        <v>31998</v>
       </c>
     </row>
     <row r="21">
@@ -8794,7 +9028,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1728</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="22">
@@ -8814,7 +9048,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>461</v>
+        <v>463299</v>
       </c>
     </row>
     <row r="23">
@@ -8834,7 +9068,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>21665</v>
       </c>
     </row>
     <row r="24">
@@ -8850,11 +9084,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Total rows for table RECEITA_DECRETO_PARCELAMENTO</t>
+          <t>Total rows for table PARCELA_S345565</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>382935</v>
       </c>
     </row>
     <row r="25">
@@ -8870,11 +9104,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Total rows for table REGIME_DECRETO_PARCELAMENTO</t>
+          <t>Total rows for table RECEITA_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
@@ -8890,10 +9124,30 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Total rows for table REGIME_DECRETO_PARCELAMENTO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MQME007</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Total rows for table TABELA_TESTE</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8908,7 +9162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8952,6 +9206,26 @@
           <t>limit</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SUGGESTED_VALUE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SUGGESTED_SOURCE</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SUGGESTED_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>SUGGESTED_DDL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8978,16 +9252,34 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MENSAGEM_DEBITO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ALTER TABLE COPAF.MENSAGEM_DEBITOS RENAME TO MENSAGEM_DEBITO;</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MQME014</t>
+          <t>MQME015</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Columns with non-standard prefixes</t>
+          <t>Columns with names longer than recommended</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8997,27 +9289,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PARCELAMENTO</t>
+          <t>DEBITO_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PER_REF_INICIO_MESES_CONSECUTIVOS</t>
+          <t>SEQ_DEBITO_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SEQ_DEBITO_DECRETO_PARCELAMENT</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ALTER TABLE COPAF.DEBITO_DECRETO_PARCELAMENTO RENAME COLUMN SEQ_DEBITO_DECRETO_PARCELAMENTO TO SEQ_DEBITO_DECRETO_PARCELAMENT;</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MQME015</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Columns with names longer than recommended</t>
+          <t>Columns without comments</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9027,31 +9341,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO_PARCELAMENTO</t>
+          <t>DEBITO_DECRETO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO_DECRETO_PARCELAMENTO</t>
+          <t>DAT_FIM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H4" t="n">
-        <v>30</v>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Data de fim.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO.DAT_FIM IS 'Data de fim.';</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MQME015</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Columns with names longer than recommended</t>
+          <t>Columns without comments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9061,20 +9389,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PARCELAMENTO</t>
+          <t>DEBITO_DECRETO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PER_REF_INICIO_MESES_CONSECUTIVOS</t>
+          <t>DAT_INICIO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>33</v>
-      </c>
-      <c r="H5" t="n">
-        <v>30</v>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Data de inicio.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO.DAT_INICIO IS 'Data de inicio.';</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -9095,17 +9437,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CNAE_DECRETO_PARCELAMENTO</t>
+          <t>DEBITO_DECRETO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>SEQ_DEBITO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sequencia de debito.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO.SEQ_DEBITO IS 'Sequencia de debito.';</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9125,17 +9485,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CNAE_DECRETO_PARCELAMENTO</t>
+          <t>DEBITO_DECRETO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COD_CAE</t>
+          <t>SEQ_DEBITO_DECRETO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sequencia de debito decreto.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO.SEQ_DEBITO_DECRETO IS 'Sequencia de debito decreto.';</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9160,12 +9538,30 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO_DECRETO</t>
+          <t>SEQ_DECRETO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sequencia de decreto.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO.SEQ_DECRETO IS 'Sequencia de decreto.';</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9190,12 +9586,30 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DAT_FIM</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sequencia de decreto parcelamento.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO.SEQ_DECRETO_PARCELAMENTO IS 'Sequencia de decreto parcelamento.';</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9220,12 +9634,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DAT_INICIO</t>
+          <t>SEQ_USUARIO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sequencia de usuario.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO.SEQ_USUARIO IS 'Sequencia de usuario.';</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9245,17 +9677,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO</t>
+          <t>DEBITO_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO</t>
+          <t>DAT_FIM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Data de fim.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO_PARCELAMENTO.DAT_FIM IS 'Data de fim.';</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9275,17 +9725,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO</t>
+          <t>DEBITO_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>DAT_INICIO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Data de inicio.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO_PARCELAMENTO.DAT_INICIO IS 'Data de inicio.';</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9305,17 +9773,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO</t>
+          <t>DEBITO_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SEQ_USUARIO</t>
+          <t>SEQ_DEBITO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sequencia de debito.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO_PARCELAMENTO.SEQ_DEBITO IS 'Sequencia de debito.';</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9346,6 +9832,24 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sequencia de debito decreto parcelamento.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO_PARCELAMENTO.SEQ_DEBITO_DECRETO_PARCELAMENTO IS 'Sequencia de debito decreto parcelamento.';</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9370,12 +9874,30 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DAT_FIM</t>
+          <t>SEQ_DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sequencia de decreto parcelamento.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO_PARCELAMENTO.SEQ_DECRETO_PARCELAMENTO IS 'Sequencia de decreto parcelamento.';</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9400,12 +9922,30 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DAT_INICIO</t>
+          <t>SEQ_USUARIO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sequencia de usuario.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DEBITO_DECRETO_PARCELAMENTO.SEQ_USUARIO IS 'Sequencia de usuario.';</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9425,17 +9965,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO_PARCELAMENTO</t>
+          <t>DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO</t>
+          <t>NUM_PERIODOS_CONSEC_ATRASO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Numero de periodos consec atraso.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DECRETO_PARCELAMENTO.NUM_PERIODOS_CONSEC_ATRASO IS 'Numero de periodos consec atraso.';</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9455,17 +10013,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO_PARCELAMENTO</t>
+          <t>DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEQ_USUARIO</t>
+          <t>STA_VERIFICA_3_MESES_CONSEC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Status de verifica 3 meses consec.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DECRETO_PARCELAMENTO.STA_VERIFICA_3_MESES_CONSEC IS 'Status de verifica 3 meses consec.';</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9485,17 +10061,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DEBITO_DECRETO_PARCELAMENTO</t>
+          <t>DECRETO_PARCELAMENTO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>TIP_LEGISLACAO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Tipo de legislacao.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.DECRETO_PARCELAMENTO.TIP_LEGISLACAO IS 'Tipo de legislacao.';</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9515,17 +10109,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DEBITO_PARCELAMENTO</t>
+          <t>FAIXA_DESCONTO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SEQ_PARCELAMENTO</t>
+          <t>DAT_FIM_ADESAO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Data de fim adesao.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.FAIXA_DESCONTO.DAT_FIM_ADESAO IS 'Data de fim adesao.';</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9545,17 +10157,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DEBITO_PARCELAMENTO</t>
+          <t>FAIXA_DESCONTO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEQ_DEBITO</t>
+          <t>DAT_INICIO_ADESAO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Data de inicio adesao.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.FAIXA_DESCONTO.DAT_INICIO_ADESAO IS 'Data de inicio adesao.';</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9575,17 +10205,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>LOG_EVENTO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
+          <t>DSC_MENSAGEM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Descricao de mensagem.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.LOG_EVENTO.DSC_MENSAGEM IS 'Descricao de mensagem.';</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9605,17 +10253,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>LOG_EVENTO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DAT_FIM</t>
+          <t>DSC_VALOR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Descricao de valor.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.LOG_EVENTO.DSC_VALOR IS 'Descricao de valor.';</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9635,17 +10301,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>MENSAGEM_DEBITOS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DAT_INICIO</t>
+          <t>DAT_MENSAGEM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Data de mensagem.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.MENSAGEM_DEBITOS.DAT_MENSAGEM IS 'Data de mensagem.';</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9665,17 +10349,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>MENSAGEM_DEBITOS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NUM_DECRETO</t>
+          <t>DSC_IDENTIFICADOR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Descricao de identificador.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.MENSAGEM_DEBITOS.DSC_IDENTIFICADOR IS 'Descricao de identificador.';</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9695,17 +10397,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>MENSAGEM_DEBITOS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>COD_ORIGEM_DECRETO</t>
+          <t>DSC_VALOR</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Descricao de valor.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.MENSAGEM_DEBITOS.DSC_VALOR IS 'Descricao de valor.';</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9725,17 +10445,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>MENSAGEM_DEBITOS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DSC_ANO_MES_PRIM_PARCELA</t>
+          <t>SEQ_MENSAGEM_DEBITOS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sequencia de mensagem debitos.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.MENSAGEM_DEBITOS.SEQ_MENSAGEM_DEBITOS IS 'Sequencia de mensagem debitos.';</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9755,17 +10493,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELAMENTO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DSC_PERIODO_REFERENCIA_FIM</t>
+          <t>SEQ_DECRETO_REFIS_A_VISTA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sequencia de decreto refis a vista.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELAMENTO.SEQ_DECRETO_REFIS_A_VISTA IS 'Sequencia de decreto refis a vista.';</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9785,17 +10541,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELAMENTO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DSC_PERIODO_REFERENCIA_INICIO</t>
+          <t>SEQ_PARCELAMENTO_ORIGINAL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sequencia de parcelamento original.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELAMENTO.SEQ_PARCELAMENTO_ORIGINAL IS 'Sequencia de parcelamento original.';</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9815,17 +10589,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>QTD_PARCELAS</t>
+          <t>COD_RECEITA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Codigo de receita.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELA_S345565.COD_RECEITA IS 'Codigo de receita.';</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9845,17 +10637,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>COD_TIPO_DECRETO</t>
+          <t>DAT_VENCIMENTO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Data de vencimento.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELA_S345565.DAT_VENCIMENTO IS 'Data de vencimento.';</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9875,17 +10685,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NUM_MAXIMO_DIAS_ATRASO</t>
+          <t>NUM_PARCELA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Numero de parcela.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELA_S345565.NUM_PARCELA IS 'Numero de parcela.';</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9905,17 +10733,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VLR_DESCONTO_JUROS</t>
+          <t>NUM_PERCENTUAL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Numero de percentual.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELA_S345565.NUM_PERCENTUAL IS 'Numero de percentual.';</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9935,17 +10781,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VLR_DESCONTO_MULTA</t>
+          <t>SEQ_DOCUMENTO_CREDITO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sequencia de documento credito.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELA_S345565.SEQ_DOCUMENTO_CREDITO IS 'Sequencia de documento credito.';</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9965,17 +10829,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>COD_TIPO_VENCIMENTO</t>
+          <t>SEQ_PARCELA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sequencia de parcela.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELA_S345565.SEQ_PARCELA IS 'Sequencia de parcela.';</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9995,17 +10877,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>PARCELA_S345565</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TIP_CRITICA_CNAE</t>
+          <t>SEQ_PARCELAMENTO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sequencia de parcelamento.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.PARCELA_S345565.SEQ_PARCELAMENTO IS 'Sequencia de parcelamento.';</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10025,2091 +10925,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DECRETO_PARCELAMENTO</t>
+          <t>TABELA_TESTE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TIP_CRITICA_RECEITA</t>
+          <t>SEQ_TABELA_TESTE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>DSC_PER_REF_INICIO_MESES_CONSE</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>COD_TIPO_ATUALIZACAO_PARCELA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>TIP_LEGISLACAO</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>STA_VERIFICA_3_MESES_CONSEC</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>NUM_PERIODOS_CONSEC_ATRASO</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DESCONTO_REFIS_DAE_MIGRADO</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>SEQ_DESCONTO_REFIS_DAE_MIGRADO</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>DESCONTO_REFIS_DAE_MIGRADO</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>VLR_DESCONTO_JUROS</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DESCONTO_REFIS_DAE_MIGRADO</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>VLR_DESCONTO_MULTA</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>DESCONTO_REFIS_DAE_MIGRADO</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>VLR_DESCONTO_PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>DESCONTO_REFIS_DAE_MIGRADO</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>SEQ_DOCUMENTO_CREDITO</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>SEQ_FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>NUM_QUANTIDADE_MAX_PARCELAS</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>NUM_QUANTIDADE_MIN_PARCELAS</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>VLR_DESCONTO_JUROS</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>VLR_DESCONTO_MULTA</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>DAT_FIM_ADESAO</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>FAIXA_DESCONTO</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>DAT_INICIO_ADESAO</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>FAIXA_PERCENTUAL_1A_PARCELA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>SEQ_FAIXA_PERC_1A_PARCELA</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FAIXA_PERCENTUAL_1A_PARCELA</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>VLR_PERCENTUAL_1A_PARCELA</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>FAIXA_PERCENTUAL_1A_PARCELA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>NUM_QUANTIDADE_MAX_PARCELAS</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>FAIXA_PERCENTUAL_1A_PARCELA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>NUM_QUANTIDADE_MIN_PARCELAS</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>FAIXA_PERCENTUAL_1A_PARCELA</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>SEQ_LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>DAT_LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>TIP_EVENTO</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>SEQ_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>SEQ_USUARIO</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>DSC_VALOR</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>LOG_EVENTO</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>DSC_MENSAGEM</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>MENSAGEM_DEBITOS</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>SEQ_MENSAGEM_DEBITOS</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>MENSAGEM_DEBITOS</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>DAT_MENSAGEM</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>MENSAGEM_DEBITOS</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>DSC_IDENTIFICADOR</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>MENSAGEM_DEBITOS</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>DSC_VALOR</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SEQ_PARCELA</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>DAT_VENCIMENTO</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>NUM_PARCELA</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>NUM_PERCENTUAL</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>COD_RECEITA</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>SEQ_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>SEQ_DOCUMENTO_CREDITO</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>PARCELA</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>SEQ_DAE_EMITIDO</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>SEQ_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>DAT_ABERTURA</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>DAT_FINAL</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>NUM_PROCESSO</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>DSC_OBSERVACAO</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>QTD_PARCELAS</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>STA_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>COD_ORGAO_LOCAL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>COD_ORGAO_LOCAL_INC</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>SEQ_PESSOA</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>SEQ_SOCIO</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>STA_PARCELAMENTO_INTERNET</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>DSC_URL_TERMO_ALFRESCO</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>DSC_ID_ARQUIVO_TERMO_ALFRESCO</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>DSC_HASH_DOCUMENTO_ALFRESCO</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>PER_REF_INICIO_MESES_CONSECUTIVOS</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>NUM_TERMO_NOTIFICACAO_PERDA</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>SEQ_PARCELAMENTO_ORIGINAL</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>SEQ_DECRETO_REFIS_A_VISTA</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>RECEITA_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>RECEITA_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>COD_RECEITA</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>REGIME_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>SEQ_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>REGIME_DECRETO_PARCELAMENTO</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>COD_REGIME_RECOLHIMENTO</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>MQME008</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Columns without comments</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>TABELA_TESTE</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>SEQ_TABELA_TESTE</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>MQME011</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Total number of tables with non-standard unique key prefixes</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>COPAF</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>DEBITO_DECRETO</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>SEQ_DEBITO</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>UK_DEBITO_DECRETO_1</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sequencia de tabela teste.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>COMMENT ON COLUMN COPAF.TABELA_TESTE.SEQ_TABELA_TESTE IS 'Sequencia de tabela teste.';</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12155,7 +10999,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>93.33%</t>
+          <t>93.75%</t>
         </is>
       </c>
     </row>
@@ -12189,7 +11033,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>99.03%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -12206,7 +11050,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>98.06%</t>
+          <t>99.06%</t>
         </is>
       </c>
     </row>
@@ -12223,7 +11067,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>67.92%</t>
         </is>
       </c>
     </row>
@@ -12274,7 +11118,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -12308,7 +11152,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>86.47%</t>
+          <t>88.48%</t>
         </is>
       </c>
     </row>
